--- a/Resultados GHS - Por semana.xlsx
+++ b/Resultados GHS - Por semana.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17ab24b3b76d94b1/Desktop/Apresentação de Mídia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{125821F5-A5F2-4562-970B-E93F06AA5946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{125821F5-A5F2-4562-970B-E93F06AA5946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C46E05E6-CCBC-48A2-A729-7D18927FACEF}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{33862748-6A9A-4C49-B295-0D4C4EDCD231}"/>
   </bookViews>
@@ -180,7 +180,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,12 +196,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -247,13 +241,13 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,7 +582,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="700" row="5">
+  <wetp:taskpane dockstate="right" visibility="0" width="528" row="5">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -703,27 +697,27 @@
         <v>11</v>
       </c>
       <c r="B7" s="10">
-        <f>IFERROR(B6/B5,0)</f>
+        <f t="shared" ref="B7:G7" si="0">IFERROR(B6/B5,0)</f>
         <v>43.548022598870055</v>
       </c>
       <c r="C7" s="10">
-        <f>IFERROR(C6/C5,0)</f>
+        <f t="shared" si="0"/>
         <v>40.807017543859651</v>
       </c>
       <c r="D7" s="10">
-        <f>IFERROR(D6/D5,0)</f>
+        <f t="shared" si="0"/>
         <v>50.646153846153844</v>
       </c>
       <c r="E7" s="10">
-        <f>IFERROR(E6/E5,0)</f>
+        <f t="shared" si="0"/>
         <v>51.31707317073171</v>
       </c>
       <c r="F7" s="10">
-        <f>IFERROR(F6/F5,0)</f>
+        <f t="shared" si="0"/>
         <v>29.341463414634145</v>
       </c>
       <c r="G7" s="9">
-        <f>IFERROR(G6/G5,0)</f>
+        <f t="shared" si="0"/>
         <v>44.836448598130843</v>
       </c>
     </row>
@@ -836,12 +830,12 @@
         <v>154</v>
       </c>
       <c r="E13" s="15">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="7">
         <f>SUM(B13:F13)</f>
-        <v>567</v>
+        <v>609</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -858,12 +852,12 @@
         <v>6914</v>
       </c>
       <c r="E14" s="16">
-        <v>4770</v>
+        <v>6788</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="9">
         <f>SUM(B14:F14)</f>
-        <v>25706</v>
+        <v>27724</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -871,28 +865,28 @@
         <v>11</v>
       </c>
       <c r="B15" s="10">
-        <f>IFERROR(B14/B13,0)</f>
+        <f t="shared" ref="B15:G15" si="1">IFERROR(B14/B13,0)</f>
         <v>61.417391304347824</v>
       </c>
       <c r="C15" s="10">
-        <f>IFERROR(C14/C13,0)</f>
+        <f t="shared" si="1"/>
         <v>40.225433526011564</v>
       </c>
       <c r="D15" s="10">
-        <f>IFERROR(D14/D13,0)</f>
+        <f t="shared" si="1"/>
         <v>44.896103896103895</v>
       </c>
       <c r="E15" s="17">
-        <f>IFERROR(E14/E13,0)</f>
-        <v>38.159999999999997</v>
+        <f t="shared" si="1"/>
+        <v>40.646706586826348</v>
       </c>
       <c r="F15" s="10">
-        <f>IFERROR(F14/F13,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G15" s="9">
-        <f>IFERROR(G14/G13,0)</f>
-        <v>45.336860670194007</v>
+        <f t="shared" si="1"/>
+        <v>45.523809523809526</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -909,12 +903,12 @@
         <v>24</v>
       </c>
       <c r="E16" s="15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="7">
         <f>SUM(B16:F16)</f>
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -931,12 +925,12 @@
         <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="7">
         <f>SUM(B17:F17)</f>
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -950,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
         <v>3</v>
@@ -958,7 +952,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="7">
         <f>SUM(B18:F18)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -1017,27 +1011,27 @@
         <v>11</v>
       </c>
       <c r="B23" s="10">
-        <f>IFERROR(B22/B21,0)</f>
+        <f t="shared" ref="B23:G23" si="2">IFERROR(B22/B21,0)</f>
         <v>0</v>
       </c>
       <c r="C23" s="10">
-        <f>IFERROR(C22/C21,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D23" s="10">
-        <f>IFERROR(D22/D21,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E23" s="10">
-        <f>IFERROR(E22/E21,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F23" s="10">
-        <f>IFERROR(F22/F21,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G23" s="9">
-        <f>IFERROR(G22/G21,0)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -1139,27 +1133,27 @@
         <v>11</v>
       </c>
       <c r="B31" s="10">
-        <f>IFERROR(B30/B29,0)</f>
+        <f t="shared" ref="B31:G31" si="3">IFERROR(B30/B29,0)</f>
         <v>0</v>
       </c>
       <c r="C31" s="10">
-        <f>IFERROR(C30/C29,0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D31" s="10">
-        <f>IFERROR(D30/D29,0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E31" s="10">
-        <f>IFERROR(E30/E29,0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F31" s="10">
-        <f>IFERROR(F30/F29,0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G31" s="9">
-        <f>IFERROR(G30/G29,0)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1261,27 +1255,27 @@
         <v>11</v>
       </c>
       <c r="B39" s="10">
-        <f>IFERROR(B38/B37,0)</f>
+        <f t="shared" ref="B39:G39" si="4">IFERROR(B38/B37,0)</f>
         <v>0</v>
       </c>
       <c r="C39" s="10">
-        <f>IFERROR(C38/C37,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="D39" s="10">
-        <f>IFERROR(D38/D37,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E39" s="10">
-        <f>IFERROR(E38/E37,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="F39" s="10">
-        <f>IFERROR(F38/F37,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G39" s="9">
-        <f>IFERROR(G38/G37,0)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -1383,27 +1377,27 @@
         <v>11</v>
       </c>
       <c r="B47" s="10">
-        <f>IFERROR(B46/B45,0)</f>
+        <f t="shared" ref="B47:G47" si="5">IFERROR(B46/B45,0)</f>
         <v>0</v>
       </c>
       <c r="C47" s="10">
-        <f>IFERROR(C46/C45,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="D47" s="10">
-        <f>IFERROR(D46/D45,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E47" s="10">
-        <f>IFERROR(E46/E45,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F47" s="10">
-        <f>IFERROR(F46/F45,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G47" s="9">
-        <f>IFERROR(G46/G45,0)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
@@ -1505,27 +1499,27 @@
         <v>11</v>
       </c>
       <c r="B55" s="10">
-        <f>IFERROR(B54/B53,0)</f>
+        <f t="shared" ref="B55:G55" si="6">IFERROR(B54/B53,0)</f>
         <v>0</v>
       </c>
       <c r="C55" s="10">
-        <f>IFERROR(C54/C53,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="D55" s="10">
-        <f>IFERROR(D54/D53,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E55" s="10">
-        <f>IFERROR(E54/E53,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F55" s="10">
-        <f>IFERROR(F54/F53,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G55" s="9">
-        <f>IFERROR(G54/G53,0)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -1612,7 +1606,7 @@
         <v>28785</v>
       </c>
       <c r="D63" s="10">
-        <f>IFERROR(C63/B63,0)</f>
+        <f t="shared" ref="D63:D70" si="7">IFERROR(C63/B63,0)</f>
         <v>44.836448598130843</v>
       </c>
       <c r="E63" s="13">
@@ -1634,27 +1628,27 @@
       </c>
       <c r="B64" s="13">
         <f>G13</f>
-        <v>567</v>
+        <v>609</v>
       </c>
       <c r="C64" s="10">
         <f>G14</f>
-        <v>25706</v>
+        <v>27724</v>
       </c>
       <c r="D64" s="10">
-        <f>IFERROR(C64/B64,0)</f>
-        <v>45.336860670194007</v>
+        <f t="shared" si="7"/>
+        <v>45.523809523809526</v>
       </c>
       <c r="E64" s="13">
         <f>G16</f>
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F64" s="13">
         <f>G17</f>
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G64" s="13">
         <f>G18</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.45">
@@ -1670,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="10">
-        <f>IFERROR(C65/B65,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E65" s="13">
@@ -1699,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="D66" s="10">
-        <f>IFERROR(C66/B66,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E66" s="13">
@@ -1728,7 +1722,7 @@
         <v>0</v>
       </c>
       <c r="D67" s="10">
-        <f>IFERROR(C67/B67,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E67" s="13">
@@ -1757,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="10">
-        <f>IFERROR(C68/B68,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E68" s="13">
@@ -1786,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="10">
-        <f>IFERROR(C69/B69,0)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E69" s="13">
@@ -1808,27 +1802,27 @@
       </c>
       <c r="B70" s="7">
         <f>SUM(B63:B69)</f>
-        <v>1209</v>
+        <v>1251</v>
       </c>
       <c r="C70" s="9">
         <f>SUM(C63:C69)</f>
-        <v>54491</v>
+        <v>56509</v>
       </c>
       <c r="D70" s="9">
-        <f>IFERROR(C70/B70,0)</f>
-        <v>45.071133167907362</v>
+        <f t="shared" si="7"/>
+        <v>45.171063149480418</v>
       </c>
       <c r="E70" s="7">
         <f>SUM(E63:E69)</f>
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F70" s="7">
         <f>SUM(F63:F69)</f>
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="G70" s="7">
         <f>SUM(G63:G69)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Resultados GHS - Por semana.xlsx
+++ b/Resultados GHS - Por semana.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17ab24b3b76d94b1/Desktop/Apresentação de Mídia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{125821F5-A5F2-4562-970B-E93F06AA5946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C46E05E6-CCBC-48A2-A729-7D18927FACEF}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{125821F5-A5F2-4562-970B-E93F06AA5946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7347B549-48A2-4839-8D91-445277315956}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{33862748-6A9A-4C49-B295-0D4C4EDCD231}"/>
+    <workbookView minimized="1" xWindow="705" yWindow="705" windowWidth="16200" windowHeight="9308" xr2:uid="{33862748-6A9A-4C49-B295-0D4C4EDCD231}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -227,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -245,9 +245,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -263,6 +260,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -829,13 +830,15 @@
       <c r="D13" s="6">
         <v>154</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="6">
         <v>167</v>
       </c>
-      <c r="F13" s="6"/>
+      <c r="F13" s="6">
+        <v>45</v>
+      </c>
       <c r="G13" s="7">
         <f>SUM(B13:F13)</f>
-        <v>609</v>
+        <v>654</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
@@ -851,13 +854,15 @@
       <c r="D14" s="8">
         <v>6914</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="8">
         <v>6788</v>
       </c>
-      <c r="F14" s="8"/>
+      <c r="F14" s="8">
+        <v>2686</v>
+      </c>
       <c r="G14" s="9">
         <f>SUM(B14:F14)</f>
-        <v>27724</v>
+        <v>30410</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
@@ -876,17 +881,17 @@
         <f t="shared" si="1"/>
         <v>44.896103896103895</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="10">
         <f t="shared" si="1"/>
         <v>40.646706586826348</v>
       </c>
       <c r="F15" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>59.68888888888889</v>
       </c>
       <c r="G15" s="9">
         <f t="shared" si="1"/>
-        <v>45.523809523809526</v>
+        <v>46.498470948012233</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
@@ -902,13 +907,15 @@
       <c r="D16" s="6">
         <v>24</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="6">
         <v>22</v>
       </c>
-      <c r="F16" s="6"/>
+      <c r="F16" s="6">
+        <v>7</v>
+      </c>
       <c r="G16" s="7">
         <f>SUM(B16:F16)</f>
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -924,13 +931,15 @@
       <c r="D17" s="6">
         <v>14</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="6">
         <v>18</v>
       </c>
-      <c r="F17" s="6"/>
+      <c r="F17" s="6">
+        <v>8</v>
+      </c>
       <c r="G17" s="7">
         <f>SUM(B17:F17)</f>
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -946,13 +955,15 @@
       <c r="D18" s="6">
         <v>2</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="6">
         <v>3</v>
       </c>
-      <c r="F18" s="6"/>
+      <c r="F18" s="6">
+        <v>2</v>
+      </c>
       <c r="G18" s="7">
         <f>SUM(B18:F18)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -1628,27 +1639,27 @@
       </c>
       <c r="B64" s="13">
         <f>G13</f>
-        <v>609</v>
+        <v>654</v>
       </c>
       <c r="C64" s="10">
         <f>G14</f>
-        <v>27724</v>
+        <v>30410</v>
       </c>
       <c r="D64" s="10">
         <f t="shared" si="7"/>
-        <v>45.523809523809526</v>
+        <v>46.498470948012233</v>
       </c>
       <c r="E64" s="13">
         <f>G16</f>
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F64" s="13">
         <f>G17</f>
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G64" s="13">
         <f>G18</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.45">
@@ -1802,27 +1813,27 @@
       </c>
       <c r="B70" s="7">
         <f>SUM(B63:B69)</f>
-        <v>1251</v>
+        <v>1296</v>
       </c>
       <c r="C70" s="9">
         <f>SUM(C63:C69)</f>
-        <v>56509</v>
+        <v>59195</v>
       </c>
       <c r="D70" s="9">
         <f t="shared" si="7"/>
-        <v>45.171063149480418</v>
+        <v>45.675154320987652</v>
       </c>
       <c r="E70" s="7">
         <f>SUM(E63:E69)</f>
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F70" s="7">
         <f>SUM(F63:F69)</f>
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="G70" s="7">
         <f>SUM(G63:G69)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Resultados GHS - Por semana.xlsx
+++ b/Resultados GHS - Por semana.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17ab24b3b76d94b1/Desktop/Apresentação de Mídia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{125821F5-A5F2-4562-970B-E93F06AA5946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7347B549-48A2-4839-8D91-445277315956}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{125821F5-A5F2-4562-970B-E93F06AA5946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{135048EA-4DA7-4B42-857D-71ACD45B7F0C}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="705" yWindow="705" windowWidth="16200" windowHeight="9308" xr2:uid="{33862748-6A9A-4C49-B295-0D4C4EDCD231}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{33862748-6A9A-4C49-B295-0D4C4EDCD231}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -993,28 +993,40 @@
       <c r="A21" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
+      <c r="B21" s="6">
+        <v>134</v>
+      </c>
+      <c r="C21" s="6">
+        <v>131</v>
+      </c>
+      <c r="D21" s="6">
+        <v>217</v>
+      </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="7">
         <f>SUM(B21:F21)</f>
-        <v>0</v>
+        <v>482</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
+      <c r="B22" s="8">
+        <v>6103</v>
+      </c>
+      <c r="C22" s="8">
+        <v>6489</v>
+      </c>
+      <c r="D22" s="8">
+        <v>7091</v>
+      </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="9">
         <f>SUM(B22:F22)</f>
-        <v>0</v>
+        <v>19683</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -1023,15 +1035,15 @@
       </c>
       <c r="B23" s="10">
         <f t="shared" ref="B23:G23" si="2">IFERROR(B22/B21,0)</f>
-        <v>0</v>
+        <v>45.544776119402982</v>
       </c>
       <c r="C23" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>49.534351145038165</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>32.677419354838712</v>
       </c>
       <c r="E23" s="10">
         <f t="shared" si="2"/>
@@ -1043,49 +1055,67 @@
       </c>
       <c r="G23" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>40.836099585062243</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
+      <c r="B24" s="6">
+        <v>14</v>
+      </c>
+      <c r="C24" s="6">
+        <v>23</v>
+      </c>
+      <c r="D24" s="6">
+        <v>25</v>
+      </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
       <c r="G24" s="7">
         <f>SUM(B24:F24)</f>
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
+      <c r="B25" s="6">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>19</v>
+      </c>
+      <c r="D25" s="6">
+        <v>12</v>
+      </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="7">
         <f>SUM(B25:F25)</f>
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
+      <c r="B26" s="6">
+        <v>2</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0</v>
+      </c>
+      <c r="D26" s="6">
+        <v>2</v>
+      </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="7">
         <f>SUM(B26:F26)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -1668,27 +1698,27 @@
       </c>
       <c r="B65" s="13">
         <f>G21</f>
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="C65" s="10">
         <f>G22</f>
-        <v>0</v>
+        <v>19683</v>
       </c>
       <c r="D65" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>40.836099585062243</v>
       </c>
       <c r="E65" s="13">
         <f>G24</f>
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F65" s="13">
         <f>G25</f>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G65" s="13">
         <f>G26</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
@@ -1813,27 +1843,27 @@
       </c>
       <c r="B70" s="7">
         <f>SUM(B63:B69)</f>
-        <v>1296</v>
+        <v>1778</v>
       </c>
       <c r="C70" s="9">
         <f>SUM(C63:C69)</f>
-        <v>59195</v>
+        <v>78878</v>
       </c>
       <c r="D70" s="9">
         <f t="shared" si="7"/>
-        <v>45.675154320987652</v>
+        <v>44.363329583802027</v>
       </c>
       <c r="E70" s="7">
         <f>SUM(E63:E69)</f>
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="F70" s="7">
         <f>SUM(F63:F69)</f>
-        <v>126</v>
+        <v>168</v>
       </c>
       <c r="G70" s="7">
         <f>SUM(G63:G69)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Resultados GHS - Por semana.xlsx
+++ b/Resultados GHS - Por semana.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17ab24b3b76d94b1/Desktop/Apresentação de Mídia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{125821F5-A5F2-4562-970B-E93F06AA5946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{135048EA-4DA7-4B42-857D-71ACD45B7F0C}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{125821F5-A5F2-4562-970B-E93F06AA5946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F35E2877-ABB2-4A2B-8796-F02EFCABCA1C}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{33862748-6A9A-4C49-B295-0D4C4EDCD231}"/>
   </bookViews>
@@ -983,7 +983,7 @@
         <v>6</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>8</v>
@@ -1002,11 +1002,15 @@
       <c r="D21" s="6">
         <v>217</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
+      <c r="E21" s="6">
+        <v>206</v>
+      </c>
+      <c r="F21" s="6">
+        <v>65</v>
+      </c>
       <c r="G21" s="7">
         <f>SUM(B21:F21)</f>
-        <v>482</v>
+        <v>753</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -1022,11 +1026,15 @@
       <c r="D22" s="8">
         <v>7091</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="E22" s="6">
+        <v>7346</v>
+      </c>
+      <c r="F22" s="8">
+        <v>2967</v>
+      </c>
       <c r="G22" s="9">
         <f>SUM(B22:F22)</f>
-        <v>19683</v>
+        <v>29996</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
@@ -1047,15 +1055,15 @@
       </c>
       <c r="E23" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>35.660194174757279</v>
       </c>
       <c r="F23" s="10">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>45.646153846153844</v>
       </c>
       <c r="G23" s="9">
         <f t="shared" si="2"/>
-        <v>40.836099585062243</v>
+        <v>39.83532536520584</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -1071,11 +1079,15 @@
       <c r="D24" s="6">
         <v>25</v>
       </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
+      <c r="E24" s="6">
+        <v>27</v>
+      </c>
+      <c r="F24" s="6">
+        <v>5</v>
+      </c>
       <c r="G24" s="7">
         <f>SUM(B24:F24)</f>
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
@@ -1091,11 +1103,15 @@
       <c r="D25" s="6">
         <v>12</v>
       </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
+      <c r="E25" s="6">
+        <v>16</v>
+      </c>
+      <c r="F25" s="6">
+        <v>0</v>
+      </c>
       <c r="G25" s="7">
         <f>SUM(B25:F25)</f>
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -1111,11 +1127,15 @@
       <c r="D26" s="6">
         <v>2</v>
       </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
+      <c r="E26" s="6">
+        <v>2</v>
+      </c>
+      <c r="F26" s="6">
+        <v>1</v>
+      </c>
       <c r="G26" s="7">
         <f>SUM(B26:F26)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -1698,27 +1718,27 @@
       </c>
       <c r="B65" s="13">
         <f>G21</f>
-        <v>482</v>
+        <v>753</v>
       </c>
       <c r="C65" s="10">
         <f>G22</f>
-        <v>19683</v>
+        <v>29996</v>
       </c>
       <c r="D65" s="10">
         <f t="shared" si="7"/>
-        <v>40.836099585062243</v>
+        <v>39.83532536520584</v>
       </c>
       <c r="E65" s="13">
         <f>G24</f>
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="F65" s="13">
         <f>G25</f>
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G65" s="13">
         <f>G26</f>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
@@ -1843,27 +1863,27 @@
       </c>
       <c r="B70" s="7">
         <f>SUM(B63:B69)</f>
-        <v>1778</v>
+        <v>2049</v>
       </c>
       <c r="C70" s="9">
         <f>SUM(C63:C69)</f>
-        <v>78878</v>
+        <v>89191</v>
       </c>
       <c r="D70" s="9">
         <f t="shared" si="7"/>
-        <v>44.363329583802027</v>
+        <v>43.529038555392873</v>
       </c>
       <c r="E70" s="7">
         <f>SUM(E63:E69)</f>
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="F70" s="7">
         <f>SUM(F63:F69)</f>
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="G70" s="7">
         <f>SUM(G63:G69)</f>
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
